--- a/linear_regression/cleaned_data/nat_gas_storage_cleaned.xlsx
+++ b/linear_regression/cleaned_data/nat_gas_storage_cleaned.xlsx
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-01-2010</t>
+          <t>2010-01-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -509,7 +509,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-02-2010</t>
+          <t>2010-02-01</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-03-2010</t>
+          <t>2010-03-01</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -571,7 +571,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-04-2010</t>
+          <t>2010-04-01</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -602,7 +602,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-05-2010</t>
+          <t>2010-05-01</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -633,7 +633,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-06-2010</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -664,7 +664,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01-07-2010</t>
+          <t>2010-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -695,7 +695,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01-08-2010</t>
+          <t>2010-08-01</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -726,7 +726,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01-09-2010</t>
+          <t>2010-09-01</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -757,7 +757,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01-10-2010</t>
+          <t>2010-10-01</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -788,7 +788,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01-11-2010</t>
+          <t>2010-11-01</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01-12-2010</t>
+          <t>2010-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -850,7 +850,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01-01-2011</t>
+          <t>2011-01-01</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -881,7 +881,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01-02-2011</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -912,7 +912,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01-03-2011</t>
+          <t>2011-03-01</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01-04-2011</t>
+          <t>2011-04-01</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -974,7 +974,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01-05-2011</t>
+          <t>2011-05-01</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1005,7 +1005,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01-06-2011</t>
+          <t>2011-06-01</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1036,7 +1036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01-07-2011</t>
+          <t>2011-07-01</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1067,7 +1067,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01-08-2011</t>
+          <t>2011-08-01</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1098,7 +1098,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>01-09-2011</t>
+          <t>2011-09-01</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1129,7 +1129,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>01-10-2011</t>
+          <t>2011-10-01</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1160,7 +1160,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>01-11-2011</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1191,7 +1191,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>01-12-2011</t>
+          <t>2011-12-01</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1222,7 +1222,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>01-01-2012</t>
+          <t>2012-01-01</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1253,7 +1253,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>01-02-2012</t>
+          <t>2012-02-01</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1284,7 +1284,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>01-03-2012</t>
+          <t>2012-03-01</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1315,7 +1315,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>01-04-2012</t>
+          <t>2012-04-01</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1346,7 +1346,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>01-05-2012</t>
+          <t>2012-05-01</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -1377,7 +1377,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>01-06-2012</t>
+          <t>2012-06-01</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1408,7 +1408,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>01-07-2012</t>
+          <t>2012-07-01</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1439,7 +1439,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>01-08-2012</t>
+          <t>2012-08-01</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1470,7 +1470,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>01-09-2012</t>
+          <t>2012-09-01</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1501,7 +1501,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>01-10-2012</t>
+          <t>2012-10-01</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1532,7 +1532,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>01-11-2012</t>
+          <t>2012-11-01</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1563,7 +1563,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01-12-2012</t>
+          <t>2012-12-01</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1594,7 +1594,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01-01-2013</t>
+          <t>2013-01-01</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1625,7 +1625,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01-02-2013</t>
+          <t>2013-02-01</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1656,7 +1656,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>01-03-2013</t>
+          <t>2013-03-01</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1687,7 +1687,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>01-04-2013</t>
+          <t>2013-04-01</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1718,7 +1718,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>01-05-2013</t>
+          <t>2013-05-01</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1749,7 +1749,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>01-06-2013</t>
+          <t>2013-06-01</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1780,7 +1780,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>01-07-2013</t>
+          <t>2013-07-01</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1811,7 +1811,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>01-08-2013</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1842,7 +1842,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>01-09-2013</t>
+          <t>2013-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1873,7 +1873,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>01-10-2013</t>
+          <t>2013-10-01</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1904,7 +1904,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>01-11-2013</t>
+          <t>2013-11-01</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1935,7 +1935,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>01-12-2013</t>
+          <t>2013-12-01</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1966,7 +1966,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>01-01-2014</t>
+          <t>2014-01-01</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1997,7 +1997,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>01-02-2014</t>
+          <t>2014-02-01</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -2028,7 +2028,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>01-03-2014</t>
+          <t>2014-03-01</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -2059,7 +2059,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01-04-2014</t>
+          <t>2014-04-01</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -2090,7 +2090,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>01-05-2014</t>
+          <t>2014-05-01</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -2121,7 +2121,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>01-06-2014</t>
+          <t>2014-06-01</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -2152,7 +2152,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>01-07-2014</t>
+          <t>2014-07-01</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -2183,7 +2183,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>01-08-2014</t>
+          <t>2014-08-01</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -2214,7 +2214,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01-09-2014</t>
+          <t>2014-09-01</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -2245,7 +2245,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>01-10-2014</t>
+          <t>2014-10-01</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -2276,7 +2276,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>01-11-2014</t>
+          <t>2014-11-01</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -2307,7 +2307,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>01-12-2014</t>
+          <t>2014-12-01</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -2338,7 +2338,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>01-01-2015</t>
+          <t>2015-01-01</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -2369,7 +2369,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>01-02-2015</t>
+          <t>2015-02-01</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -2400,7 +2400,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>01-03-2015</t>
+          <t>2015-03-01</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -2431,7 +2431,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>01-04-2015</t>
+          <t>2015-04-01</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -2462,7 +2462,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>01-05-2015</t>
+          <t>2015-05-01</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -2493,7 +2493,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>01-06-2015</t>
+          <t>2015-06-01</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -2524,7 +2524,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01-07-2015</t>
+          <t>2015-07-01</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -2555,7 +2555,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>01-08-2015</t>
+          <t>2015-08-01</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -2586,7 +2586,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>01-09-2015</t>
+          <t>2015-09-01</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -2617,7 +2617,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>01-10-2015</t>
+          <t>2015-10-01</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -2648,7 +2648,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>01-11-2015</t>
+          <t>2015-11-01</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2679,7 +2679,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>01-12-2015</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -2710,7 +2710,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>01-01-2016</t>
+          <t>2016-01-01</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -2741,7 +2741,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>01-02-2016</t>
+          <t>2016-02-01</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -2772,7 +2772,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>01-03-2016</t>
+          <t>2016-03-01</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -2803,7 +2803,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>01-04-2016</t>
+          <t>2016-04-01</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -2834,7 +2834,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>01-05-2016</t>
+          <t>2016-05-01</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -2865,7 +2865,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>01-06-2016</t>
+          <t>2016-06-01</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2896,7 +2896,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>01-07-2016</t>
+          <t>2016-07-01</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2927,7 +2927,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>01-08-2016</t>
+          <t>2016-08-01</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2958,7 +2958,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>01-09-2016</t>
+          <t>2016-09-01</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -2989,7 +2989,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>01-10-2016</t>
+          <t>2016-10-01</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -3020,7 +3020,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>01-11-2016</t>
+          <t>2016-11-01</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -3051,7 +3051,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>01-12-2016</t>
+          <t>2016-12-01</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -3082,7 +3082,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>01-01-2017</t>
+          <t>2017-01-01</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -3113,7 +3113,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>01-02-2017</t>
+          <t>2017-02-01</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -3144,7 +3144,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>01-03-2017</t>
+          <t>2017-03-01</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -3175,7 +3175,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>01-04-2017</t>
+          <t>2017-04-01</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -3206,7 +3206,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>01-05-2017</t>
+          <t>2017-05-01</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -3237,7 +3237,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>01-06-2017</t>
+          <t>2017-06-01</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -3268,7 +3268,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>01-07-2017</t>
+          <t>2017-07-01</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -3299,7 +3299,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>01-08-2017</t>
+          <t>2017-08-01</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -3330,7 +3330,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>01-09-2017</t>
+          <t>2017-09-01</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -3361,7 +3361,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>01-10-2017</t>
+          <t>2017-10-01</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -3392,7 +3392,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>01-11-2017</t>
+          <t>2017-11-01</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -3423,7 +3423,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>01-12-2017</t>
+          <t>2017-12-01</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -3454,7 +3454,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>01-01-2018</t>
+          <t>2018-01-01</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -3485,7 +3485,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>01-02-2018</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -3516,7 +3516,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>01-03-2018</t>
+          <t>2018-03-01</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -3547,7 +3547,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>01-04-2018</t>
+          <t>2018-04-01</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -3578,7 +3578,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>01-05-2018</t>
+          <t>2018-05-01</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -3609,7 +3609,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>01-06-2018</t>
+          <t>2018-06-01</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -3640,7 +3640,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>01-07-2018</t>
+          <t>2018-07-01</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -3671,7 +3671,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>01-08-2018</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -3702,7 +3702,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>01-09-2018</t>
+          <t>2018-09-01</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -3733,7 +3733,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>01-10-2018</t>
+          <t>2018-10-01</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -3764,7 +3764,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>01-11-2018</t>
+          <t>2018-11-01</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -3795,7 +3795,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>01-12-2018</t>
+          <t>2018-12-01</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -3826,7 +3826,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>01-01-2019</t>
+          <t>2019-01-01</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -3857,7 +3857,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>01-02-2019</t>
+          <t>2019-02-01</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -3888,7 +3888,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>01-03-2019</t>
+          <t>2019-03-01</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -3919,7 +3919,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>01-04-2019</t>
+          <t>2019-04-01</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -3950,7 +3950,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>01-05-2019</t>
+          <t>2019-05-01</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -3981,7 +3981,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>01-06-2019</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -4012,7 +4012,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>01-07-2019</t>
+          <t>2019-07-01</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -4043,7 +4043,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>01-08-2019</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -4074,7 +4074,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>01-09-2019</t>
+          <t>2019-09-01</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -4105,7 +4105,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>01-10-2019</t>
+          <t>2019-10-01</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -4136,7 +4136,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>01-11-2019</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -4167,7 +4167,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>01-12-2019</t>
+          <t>2019-12-01</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -4198,7 +4198,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>01-01-2020</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -4229,7 +4229,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>01-02-2020</t>
+          <t>2020-02-01</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -4260,7 +4260,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>01-03-2020</t>
+          <t>2020-03-01</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -4291,7 +4291,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>01-04-2020</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -4322,7 +4322,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>01-05-2020</t>
+          <t>2020-05-01</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -4353,7 +4353,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>01-06-2020</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -4384,7 +4384,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>01-07-2020</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -4415,7 +4415,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>01-08-2020</t>
+          <t>2020-08-01</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -4446,7 +4446,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>01-09-2020</t>
+          <t>2020-09-01</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -4477,7 +4477,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>01-10-2020</t>
+          <t>2020-10-01</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -4508,7 +4508,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>01-11-2020</t>
+          <t>2020-11-01</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -4539,7 +4539,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>01-12-2020</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -4570,7 +4570,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>01-01-2021</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -4601,7 +4601,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>01-02-2021</t>
+          <t>2021-02-01</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -4632,7 +4632,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>01-03-2021</t>
+          <t>2021-03-01</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -4663,7 +4663,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>01-04-2021</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -4694,7 +4694,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>01-05-2021</t>
+          <t>2021-05-01</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -4725,7 +4725,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>01-06-2021</t>
+          <t>2021-06-01</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -4756,7 +4756,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>01-07-2021</t>
+          <t>2021-07-01</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -4787,7 +4787,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>01-08-2021</t>
+          <t>2021-08-01</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -4818,7 +4818,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>01-09-2021</t>
+          <t>2021-09-01</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -4849,7 +4849,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>01-10-2021</t>
+          <t>2021-10-01</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -4880,7 +4880,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>01-11-2021</t>
+          <t>2021-11-01</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -4911,7 +4911,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>01-12-2021</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -4942,7 +4942,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>01-01-2022</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -4973,7 +4973,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>01-02-2022</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -5004,7 +5004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>01-03-2022</t>
+          <t>2022-03-01</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -5035,7 +5035,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>01-04-2022</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -5066,7 +5066,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>01-05-2022</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -5097,7 +5097,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>01-06-2022</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -5128,7 +5128,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>01-07-2022</t>
+          <t>2022-07-01</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -5159,7 +5159,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>01-08-2022</t>
+          <t>2022-08-01</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -5190,7 +5190,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>01-09-2022</t>
+          <t>2022-09-01</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -5221,7 +5221,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>01-10-2022</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -5252,7 +5252,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>01-11-2022</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -5283,7 +5283,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>01-12-2022</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -5314,7 +5314,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>01-01-2023</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -5345,7 +5345,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>01-02-2023</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -5376,7 +5376,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>01-03-2023</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -5407,7 +5407,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>01-04-2023</t>
+          <t>2023-04-01</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -5438,7 +5438,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>01-05-2023</t>
+          <t>2023-05-01</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -5469,7 +5469,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>01-06-2023</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -5500,7 +5500,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>01-07-2023</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -5531,7 +5531,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>01-08-2023</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -5562,7 +5562,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>01-09-2023</t>
+          <t>2023-09-01</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -5593,7 +5593,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>01-10-2023</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -5624,7 +5624,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>01-11-2023</t>
+          <t>2023-11-01</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -5655,7 +5655,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>01-12-2023</t>
+          <t>2023-12-01</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -5686,7 +5686,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>01-01-2024</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -5717,7 +5717,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>01-02-2024</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -5748,7 +5748,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>01-03-2024</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -5779,7 +5779,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>01-04-2024</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -5810,7 +5810,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>01-05-2024</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -5841,7 +5841,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>01-06-2024</t>
+          <t>2024-06-01</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -5872,7 +5872,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>01-07-2024</t>
+          <t>2024-07-01</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -5903,7 +5903,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>01-08-2024</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -5934,7 +5934,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>01-09-2024</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -5965,7 +5965,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>01-10-2024</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -5996,7 +5996,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>01-11-2024</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -6027,7 +6027,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>01-12-2024</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -6058,7 +6058,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>01-01-2025</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -6089,7 +6089,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>01-02-2025</t>
+          <t>2025-02-01</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -6120,7 +6120,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>01-03-2025</t>
+          <t>2025-03-01</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -6151,7 +6151,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>01-04-2025</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -6182,7 +6182,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>01-05-2025</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -6213,7 +6213,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>01-06-2025</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -6244,7 +6244,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>01-07-2025</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -6275,7 +6275,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>01-08-2025</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -6306,7 +6306,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>01-09-2025</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -6337,7 +6337,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>01-10-2025</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -6368,7 +6368,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>01-11-2025</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -6399,7 +6399,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>01-12-2025</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -6430,7 +6430,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>01-01-2026</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -6461,7 +6461,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>01-02-2026</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -6492,7 +6492,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>01-03-2026</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -6523,7 +6523,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>01-04-2026</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -6554,7 +6554,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>01-05-2026</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -6585,7 +6585,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -6616,7 +6616,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>01-07-2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -6647,7 +6647,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -6678,7 +6678,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B202" t="n">
